--- a/Financials Mapping.xlsx
+++ b/Financials Mapping.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Avinash Agaewal\OneDrive - Lords Education &amp; Health Society\Desktop\FINANCIALS\AUTO FIN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Avinash Agaewal\OneDrive - Lords Education &amp; Health Society\Desktop\REPORT\MAPPINGS UPLOAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8058301F-EA84-4769-AEC7-12388965AAF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FA2A72-F333-47C5-846F-75EA84F2115F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F90151BA-C1C7-44FD-8554-839FB031CC7B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1014</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1015</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3042" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3045" uniqueCount="307">
   <si>
     <t>Account Name</t>
   </si>
@@ -1014,9 +1014,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1331,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D54E5C-9537-4F35-B0F6-F61D64093053}">
-  <dimension ref="A1:C1014"/>
+  <dimension ref="A1:C1015"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.77734375" bestFit="1" customWidth="1"/>
@@ -12493,8 +12494,19 @@
         <v>222</v>
       </c>
     </row>
+    <row r="1015" spans="1:3" ht="16.2" x14ac:dyDescent="0.4">
+      <c r="A1015" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1015" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1015" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C1014" xr:uid="{65D54E5C-9537-4F35-B0F6-F61D64093053}"/>
+  <autoFilter ref="A1:C1015" xr:uid="{65D54E5C-9537-4F35-B0F6-F61D64093053}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>